--- a/assets/PanglaoDB/celltypes.xlsx
+++ b/assets/PanglaoDB/celltypes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\scGEAToolbox\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\claude_dev\scGEAToolbox_dev\assets\PanglaoDB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C10C6D8-89B8-401C-8236-F2D4145573D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8959E368-AE18-42B7-822A-B00420A11775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51480" yWindow="-120" windowWidth="30960" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10092" yWindow="2964" windowWidth="30960" windowHeight="12120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="human" sheetId="1" r:id="rId1"/>
@@ -400,9 +400,6 @@
     <t>DRD2,NOS1,PHOX2B,TH,HMOX2,NDUFA4L2,COX4I2,IL1R1,TNFRSF1A,CTH,CBS,GJA1,KCNK3,ASIC1,ASIC3,CALD1,COL4A1,VIM,EPAS1,GFRA1,GFRA2,GAP43,MMP9,IL6ST,KCNJ11,KCNJ8,ABCC8,KCNK9</t>
   </si>
   <si>
-    <t>Glutaminergic neurons</t>
-  </si>
-  <si>
     <t>SLC17A7,SLC17A6,GRIN1,GRIN2B,GLS,MEIS2,SLC17A8,SLC1A1,SLC1A2,SLC1A6</t>
   </si>
   <si>
@@ -1129,9 +1126,6 @@
     <t>Sox1,Sox2,Nestin,Cd133</t>
   </si>
   <si>
-    <t>Alpha cells [PMID:35440614] ALDH1A1.B2M,CFC1,CLU,CRYBA2,CYSTM1,DPP4,F10,AFP,FXYD3,FXYD5,GC,GCG,GLS,GPX3,HIGD1A,HLA-A,HAL-E,IR2,ITGB1,KCTD12,LOXL4,MUC13,NAA20,PALLD,PAPPA2,PCSK2,PEMT,PLCE1,PLIN3,RGS4,RNASEK,SLC7A2,SMIM24,SPINT2,TM4SF4,TMEM176A,TMEM176B,TTR,VGF,</t>
-  </si>
-  <si>
     <t>PanglaoDB </t>
   </si>
   <si>
@@ -1550,6 +1544,12 @@
   </si>
   <si>
     <t>Mural cells [PMID:32769974]</t>
+  </si>
+  <si>
+    <t>Glutamatergic neurons</t>
+  </si>
+  <si>
+    <t>ALDH1A1.B2M,CFC1,CLU,CRYBA2,CYSTM1,DPP4,F10,AFP,FXYD3,FXYD5,GC,GCG,GLS,GPX3,HIGD1A,HLA-A,HAL-E,IR2,ITGB1,KCTD12,LOXL4,MUC13,NAA20,PALLD,PAPPA2,PCSK2,PEMT,PLCE1,PLIN3,RGS4,RNASEK,SLC7A2,SMIM24,SPINT2,TM4SF4,TMEM176A,TMEM176B,TTR,VGF,</t>
   </si>
 </sst>
 </file>
@@ -1927,7 +1927,7 @@
   <dimension ref="A1:E183"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.21875" customWidth="1"/>
+    <col min="1" max="1" width="27.33203125" customWidth="1"/>
     <col min="2" max="2" width="48.5546875" style="2" customWidth="1"/>
     <col min="3" max="3" width="64.5546875" style="3" customWidth="1"/>
     <col min="4" max="4" width="28.6640625" customWidth="1"/>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="C2" s="5"/>
       <c r="D2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E2" s="1"/>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="C3" s="5"/>
       <c r="D3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="C4" s="5"/>
       <c r="D4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1996,7 +1996,7 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -2007,7 +2007,7 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -2018,7 +2018,7 @@
         <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -2029,7 +2029,7 @@
         <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -2040,7 +2040,7 @@
         <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -2051,7 +2051,7 @@
         <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -2062,7 +2062,7 @@
         <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -2073,7 +2073,7 @@
         <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -2084,7 +2084,7 @@
         <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -2095,7 +2095,7 @@
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -2106,7 +2106,7 @@
         <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -2117,7 +2117,7 @@
         <v>35</v>
       </c>
       <c r="D16" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -2128,7 +2128,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -2139,7 +2139,7 @@
         <v>39</v>
       </c>
       <c r="D18" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -2150,7 +2150,7 @@
         <v>41</v>
       </c>
       <c r="D19" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -2161,7 +2161,7 @@
         <v>43</v>
       </c>
       <c r="D20" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -2172,7 +2172,7 @@
         <v>45</v>
       </c>
       <c r="D21" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -2183,7 +2183,7 @@
         <v>47</v>
       </c>
       <c r="D22" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -2194,7 +2194,7 @@
         <v>49</v>
       </c>
       <c r="D23" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -2205,7 +2205,7 @@
         <v>51</v>
       </c>
       <c r="D24" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -2216,7 +2216,7 @@
         <v>53</v>
       </c>
       <c r="D25" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -2227,7 +2227,7 @@
         <v>55</v>
       </c>
       <c r="D26" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -2238,7 +2238,7 @@
         <v>57</v>
       </c>
       <c r="D27" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -2249,7 +2249,7 @@
         <v>59</v>
       </c>
       <c r="D28" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -2260,7 +2260,7 @@
         <v>61</v>
       </c>
       <c r="D29" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -2271,7 +2271,7 @@
         <v>63</v>
       </c>
       <c r="D30" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -2282,7 +2282,7 @@
         <v>65</v>
       </c>
       <c r="D31" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -2293,7 +2293,7 @@
         <v>67</v>
       </c>
       <c r="D32" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -2304,7 +2304,7 @@
         <v>69</v>
       </c>
       <c r="D33" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -2315,7 +2315,7 @@
         <v>71</v>
       </c>
       <c r="D34" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -2326,7 +2326,7 @@
         <v>73</v>
       </c>
       <c r="D35" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -2337,7 +2337,7 @@
         <v>75</v>
       </c>
       <c r="D36" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -2348,7 +2348,7 @@
         <v>77</v>
       </c>
       <c r="D37" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -2359,7 +2359,7 @@
         <v>79</v>
       </c>
       <c r="D38" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -2370,7 +2370,7 @@
         <v>81</v>
       </c>
       <c r="D39" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -2381,7 +2381,7 @@
         <v>83</v>
       </c>
       <c r="D40" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -2392,7 +2392,7 @@
         <v>85</v>
       </c>
       <c r="D41" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -2403,7 +2403,7 @@
         <v>87</v>
       </c>
       <c r="D42" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -2414,7 +2414,7 @@
         <v>89</v>
       </c>
       <c r="D43" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -2425,7 +2425,7 @@
         <v>91</v>
       </c>
       <c r="D44" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -2436,7 +2436,7 @@
         <v>93</v>
       </c>
       <c r="D45" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -2447,7 +2447,7 @@
         <v>95</v>
       </c>
       <c r="D46" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -2458,7 +2458,7 @@
         <v>97</v>
       </c>
       <c r="D47" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -2469,7 +2469,7 @@
         <v>99</v>
       </c>
       <c r="D48" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -2480,7 +2480,7 @@
         <v>101</v>
       </c>
       <c r="D49" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -2491,7 +2491,7 @@
         <v>103</v>
       </c>
       <c r="D50" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -2502,7 +2502,7 @@
         <v>105</v>
       </c>
       <c r="D51" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -2513,7 +2513,7 @@
         <v>107</v>
       </c>
       <c r="D52" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -2524,7 +2524,7 @@
         <v>109</v>
       </c>
       <c r="D53" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -2535,7 +2535,7 @@
         <v>111</v>
       </c>
       <c r="D54" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -2546,7 +2546,7 @@
         <v>113</v>
       </c>
       <c r="D55" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -2557,7 +2557,7 @@
         <v>115</v>
       </c>
       <c r="D56" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -2568,7 +2568,7 @@
         <v>117</v>
       </c>
       <c r="D57" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
@@ -2579,7 +2579,7 @@
         <v>119</v>
       </c>
       <c r="D58" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -2590,7 +2590,7 @@
         <v>121</v>
       </c>
       <c r="D59" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -2601,260 +2601,260 @@
         <v>123</v>
       </c>
       <c r="D60" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>506</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="D61" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>125</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="D62" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>127</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="D63" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>129</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="D64" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>131</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="D65" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
+        <v>133</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="D66" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
+        <v>135</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="D67" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>137</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="D68" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>139</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="D69" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>141</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="D70" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>143</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="D71" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>145</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="D72" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>147</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>149</v>
-      </c>
       <c r="D73" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>149</v>
+      </c>
+      <c r="B74" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>151</v>
-      </c>
       <c r="D74" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>151</v>
+      </c>
+      <c r="B75" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="D75" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>153</v>
+      </c>
+      <c r="B76" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="D76" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
+        <v>155</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>157</v>
-      </c>
       <c r="D77" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>157</v>
+      </c>
+      <c r="B78" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="D78" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>159</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="D79" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>161</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>163</v>
-      </c>
       <c r="D80" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>163</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="D81" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
+        <v>165</v>
+      </c>
+      <c r="B82" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="D82" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
+        <v>167</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>169</v>
-      </c>
       <c r="D83" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -2862,1099 +2862,1099 @@
         <v>5</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D84" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
+        <v>170</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>172</v>
-      </c>
       <c r="D85" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
+        <v>172</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>174</v>
-      </c>
       <c r="D86" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
+        <v>174</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>176</v>
-      </c>
       <c r="D87" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
+        <v>176</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="D88" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>178</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>180</v>
-      </c>
       <c r="D89" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
+        <v>180</v>
+      </c>
+      <c r="B90" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>182</v>
-      </c>
       <c r="D90" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
+        <v>182</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="D91" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
+        <v>184</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>186</v>
-      </c>
       <c r="D92" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
+        <v>186</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>188</v>
-      </c>
       <c r="D93" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
+        <v>188</v>
+      </c>
+      <c r="B94" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>190</v>
-      </c>
       <c r="D94" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
+        <v>190</v>
+      </c>
+      <c r="B95" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="D95" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
+        <v>192</v>
+      </c>
+      <c r="B96" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>194</v>
-      </c>
       <c r="D96" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
+        <v>194</v>
+      </c>
+      <c r="B97" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>196</v>
-      </c>
       <c r="D97" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
+        <v>196</v>
+      </c>
+      <c r="B98" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>198</v>
-      </c>
       <c r="D98" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
+        <v>198</v>
+      </c>
+      <c r="B99" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>200</v>
-      </c>
       <c r="D99" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
+        <v>200</v>
+      </c>
+      <c r="B100" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B100" s="2" t="s">
-        <v>202</v>
-      </c>
       <c r="D100" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
+        <v>202</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>204</v>
-      </c>
       <c r="D101" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
+        <v>204</v>
+      </c>
+      <c r="B102" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>206</v>
-      </c>
       <c r="D102" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
+        <v>206</v>
+      </c>
+      <c r="B103" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="D103" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
+        <v>208</v>
+      </c>
+      <c r="B104" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>210</v>
-      </c>
       <c r="D104" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
+        <v>210</v>
+      </c>
+      <c r="B105" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>212</v>
-      </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
+        <v>212</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B106" s="2" t="s">
-        <v>214</v>
-      </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
+        <v>214</v>
+      </c>
+      <c r="B107" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>216</v>
-      </c>
       <c r="D107" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
+        <v>216</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="D108" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
+        <v>218</v>
+      </c>
+      <c r="B109" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="B109" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="D109" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
+        <v>220</v>
+      </c>
+      <c r="B110" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>222</v>
-      </c>
       <c r="D110" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
+        <v>222</v>
+      </c>
+      <c r="B111" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="D111" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
+        <v>224</v>
+      </c>
+      <c r="B112" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B112" s="2" t="s">
-        <v>226</v>
-      </c>
       <c r="D112" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
+        <v>226</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B113" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="D113" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
+        <v>228</v>
+      </c>
+      <c r="B114" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="B114" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="D114" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
+        <v>230</v>
+      </c>
+      <c r="B115" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B115" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="D115" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
+        <v>232</v>
+      </c>
+      <c r="B116" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="B116" s="2" t="s">
-        <v>234</v>
-      </c>
       <c r="D116" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
+        <v>234</v>
+      </c>
+      <c r="B117" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="B117" s="2" t="s">
-        <v>236</v>
-      </c>
       <c r="D117" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
+        <v>236</v>
+      </c>
+      <c r="B118" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="B118" s="2" t="s">
-        <v>238</v>
-      </c>
       <c r="D118" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
+        <v>238</v>
+      </c>
+      <c r="B119" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B119" s="2" t="s">
-        <v>240</v>
-      </c>
       <c r="D119" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
+        <v>240</v>
+      </c>
+      <c r="B120" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>242</v>
-      </c>
       <c r="D120" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
+        <v>242</v>
+      </c>
+      <c r="B121" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B121" s="2" t="s">
-        <v>244</v>
-      </c>
       <c r="D121" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
+        <v>244</v>
+      </c>
+      <c r="B122" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>246</v>
-      </c>
       <c r="D122" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
+        <v>246</v>
+      </c>
+      <c r="B123" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>248</v>
-      </c>
       <c r="D123" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
+        <v>248</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>250</v>
-      </c>
       <c r="D124" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
+        <v>250</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B125" s="2" t="s">
-        <v>252</v>
-      </c>
       <c r="D125" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
+        <v>252</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>254</v>
-      </c>
       <c r="D126" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
+        <v>254</v>
+      </c>
+      <c r="B127" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B127" s="2" t="s">
-        <v>256</v>
-      </c>
       <c r="D127" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
+        <v>256</v>
+      </c>
+      <c r="B128" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="D128" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
+        <v>258</v>
+      </c>
+      <c r="B129" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B129" s="2" t="s">
-        <v>260</v>
-      </c>
       <c r="D129" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
+        <v>260</v>
+      </c>
+      <c r="B130" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B130" s="2" t="s">
-        <v>262</v>
-      </c>
       <c r="D130" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
+        <v>262</v>
+      </c>
+      <c r="B131" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="B131" s="2" t="s">
-        <v>264</v>
-      </c>
       <c r="D131" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
+        <v>264</v>
+      </c>
+      <c r="B132" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B132" s="2" t="s">
-        <v>266</v>
-      </c>
       <c r="D132" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
+        <v>266</v>
+      </c>
+      <c r="B133" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B133" s="2" t="s">
-        <v>268</v>
-      </c>
       <c r="D133" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
+        <v>268</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B134" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="D134" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
+        <v>270</v>
+      </c>
+      <c r="B135" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B135" s="2" t="s">
-        <v>272</v>
-      </c>
       <c r="D135" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
+        <v>272</v>
+      </c>
+      <c r="B136" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="B136" s="2" t="s">
-        <v>274</v>
-      </c>
       <c r="D136" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
+        <v>274</v>
+      </c>
+      <c r="B137" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B137" s="2" t="s">
-        <v>276</v>
-      </c>
       <c r="D137" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
+        <v>276</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B138" s="2" t="s">
-        <v>278</v>
-      </c>
       <c r="D138" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
+        <v>278</v>
+      </c>
+      <c r="B139" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="B139" s="2" t="s">
-        <v>280</v>
-      </c>
       <c r="D139" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
+        <v>280</v>
+      </c>
+      <c r="B140" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="B140" s="2" t="s">
-        <v>282</v>
-      </c>
       <c r="D140" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
+        <v>282</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="B141" s="2" t="s">
-        <v>284</v>
-      </c>
       <c r="D141" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
+        <v>284</v>
+      </c>
+      <c r="B142" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="B142" s="2" t="s">
-        <v>286</v>
-      </c>
       <c r="D142" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
+        <v>286</v>
+      </c>
+      <c r="B143" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B143" s="2" t="s">
-        <v>288</v>
-      </c>
       <c r="D143" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
+        <v>288</v>
+      </c>
+      <c r="B144" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="B144" s="2" t="s">
-        <v>290</v>
-      </c>
       <c r="D144" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
+        <v>290</v>
+      </c>
+      <c r="B145" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="B145" s="2" t="s">
-        <v>292</v>
-      </c>
       <c r="D145" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
+        <v>292</v>
+      </c>
+      <c r="B146" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="B146" s="2" t="s">
-        <v>294</v>
-      </c>
       <c r="D146" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
+        <v>294</v>
+      </c>
+      <c r="B147" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="B147" s="2" t="s">
-        <v>296</v>
-      </c>
       <c r="D147" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
+        <v>296</v>
+      </c>
+      <c r="B148" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="B148" s="2" t="s">
-        <v>298</v>
-      </c>
       <c r="D148" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
+        <v>298</v>
+      </c>
+      <c r="B149" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="B149" s="2" t="s">
-        <v>300</v>
-      </c>
       <c r="D149" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
+        <v>300</v>
+      </c>
+      <c r="B150" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="B150" s="2" t="s">
-        <v>302</v>
-      </c>
       <c r="D150" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
+        <v>302</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B151" s="2" t="s">
-        <v>304</v>
-      </c>
       <c r="D151" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
+        <v>304</v>
+      </c>
+      <c r="B152" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="B152" s="2" t="s">
-        <v>306</v>
-      </c>
       <c r="D152" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
+        <v>306</v>
+      </c>
+      <c r="B153" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="B153" s="2" t="s">
-        <v>308</v>
-      </c>
       <c r="D153" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
+        <v>308</v>
+      </c>
+      <c r="B154" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B154" s="2" t="s">
-        <v>310</v>
-      </c>
       <c r="D154" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
+        <v>310</v>
+      </c>
+      <c r="B155" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="B155" s="2" t="s">
-        <v>312</v>
-      </c>
       <c r="D155" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
+        <v>312</v>
+      </c>
+      <c r="B156" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="B156" s="2" t="s">
-        <v>314</v>
-      </c>
       <c r="D156" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
+        <v>314</v>
+      </c>
+      <c r="B157" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="B157" s="2" t="s">
-        <v>316</v>
-      </c>
       <c r="D157" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
+        <v>316</v>
+      </c>
+      <c r="B158" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="B158" s="2" t="s">
-        <v>318</v>
-      </c>
       <c r="D158" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
+        <v>318</v>
+      </c>
+      <c r="B159" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="B159" s="2" t="s">
-        <v>320</v>
-      </c>
       <c r="D159" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
+        <v>320</v>
+      </c>
+      <c r="B160" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="B160" s="2" t="s">
-        <v>322</v>
-      </c>
       <c r="D160" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
+        <v>322</v>
+      </c>
+      <c r="B161" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="B161" s="2" t="s">
-        <v>324</v>
-      </c>
       <c r="D161" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
+        <v>324</v>
+      </c>
+      <c r="B162" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B162" s="2" t="s">
-        <v>326</v>
-      </c>
       <c r="D162" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
+        <v>326</v>
+      </c>
+      <c r="B163" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="B163" s="2" t="s">
-        <v>328</v>
-      </c>
       <c r="D163" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
+        <v>328</v>
+      </c>
+      <c r="B164" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="B164" s="2" t="s">
-        <v>330</v>
-      </c>
       <c r="D164" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
+        <v>330</v>
+      </c>
+      <c r="B165" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B165" s="2" t="s">
-        <v>332</v>
-      </c>
       <c r="D165" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
+        <v>332</v>
+      </c>
+      <c r="B166" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="B166" s="2" t="s">
-        <v>334</v>
-      </c>
       <c r="D166" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
+        <v>334</v>
+      </c>
+      <c r="B167" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="B167" s="2" t="s">
-        <v>336</v>
-      </c>
       <c r="D167" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
+        <v>336</v>
+      </c>
+      <c r="B168" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="B168" s="2" t="s">
-        <v>338</v>
-      </c>
       <c r="D168" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
+        <v>338</v>
+      </c>
+      <c r="B169" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="B169" s="2" t="s">
-        <v>340</v>
-      </c>
       <c r="D169" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
+        <v>340</v>
+      </c>
+      <c r="B170" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="B170" s="2" t="s">
-        <v>342</v>
-      </c>
       <c r="D170" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
+        <v>342</v>
+      </c>
+      <c r="B171" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="B171" s="2" t="s">
-        <v>344</v>
-      </c>
       <c r="D171" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
+        <v>344</v>
+      </c>
+      <c r="B172" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="B172" s="2" t="s">
-        <v>346</v>
-      </c>
       <c r="D172" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
+        <v>346</v>
+      </c>
+      <c r="B173" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B173" s="2" t="s">
-        <v>348</v>
-      </c>
       <c r="D173" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
+        <v>348</v>
+      </c>
+      <c r="B174" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="B174" s="2" t="s">
-        <v>350</v>
-      </c>
       <c r="D174" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
+        <v>350</v>
+      </c>
+      <c r="B175" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="B175" s="2" t="s">
-        <v>352</v>
-      </c>
       <c r="D175" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
+        <v>352</v>
+      </c>
+      <c r="B176" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="B176" s="2" t="s">
-        <v>354</v>
-      </c>
       <c r="D176" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
+        <v>354</v>
+      </c>
+      <c r="B177" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="B177" s="2" t="s">
-        <v>356</v>
-      </c>
       <c r="D177" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
+        <v>356</v>
+      </c>
+      <c r="B178" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="B178" s="2" t="s">
-        <v>358</v>
-      </c>
       <c r="D178" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
+        <v>358</v>
+      </c>
+      <c r="B179" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="B179" s="2" t="s">
-        <v>360</v>
-      </c>
       <c r="D179" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
+        <v>360</v>
+      </c>
+      <c r="B180" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B180" s="2" t="s">
-        <v>362</v>
-      </c>
       <c r="D180" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
+        <v>362</v>
+      </c>
+      <c r="B181" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="B181" s="2" t="s">
-        <v>364</v>
-      </c>
       <c r="D181" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
+        <v>364</v>
+      </c>
+      <c r="B182" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="B182" s="2" t="s">
-        <v>366</v>
-      </c>
       <c r="D182" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>367</v>
+        <v>507</v>
       </c>
       <c r="D183" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -3968,7 +3968,7 @@
   <dimension ref="A1:E187"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="41.77734375" customWidth="1"/>
+    <col min="1" max="1" width="41.6640625" customWidth="1"/>
     <col min="2" max="2" width="48.5546875" style="2" customWidth="1"/>
     <col min="3" max="3" width="64.5546875" style="3" customWidth="1"/>
     <col min="4" max="4" width="28.6640625" customWidth="1"/>
@@ -3997,11 +3997,11 @@
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E2" s="1"/>
     </row>
@@ -4010,11 +4010,11 @@
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -4022,11 +4022,11 @@
         <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -4037,7 +4037,7 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -4048,7 +4048,7 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -4056,10 +4056,10 @@
         <v>16</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -4070,7 +4070,7 @@
         <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -4078,10 +4078,10 @@
         <v>20</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D9" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -4089,10 +4089,10 @@
         <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D10" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -4100,10 +4100,10 @@
         <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D11" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -4114,7 +4114,7 @@
         <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -4122,10 +4122,10 @@
         <v>28</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D13" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -4133,10 +4133,10 @@
         <v>30</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D14" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -4144,10 +4144,10 @@
         <v>32</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -4155,10 +4155,10 @@
         <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D16" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -4166,10 +4166,10 @@
         <v>36</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D17" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -4180,7 +4180,7 @@
         <v>39</v>
       </c>
       <c r="D18" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -4188,10 +4188,10 @@
         <v>40</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D19" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -4199,10 +4199,10 @@
         <v>42</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D20" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -4210,10 +4210,10 @@
         <v>44</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D21" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -4221,10 +4221,10 @@
         <v>46</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D22" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -4232,10 +4232,10 @@
         <v>48</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D23" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -4246,7 +4246,7 @@
         <v>51</v>
       </c>
       <c r="D24" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -4254,10 +4254,10 @@
         <v>52</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D25" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -4265,10 +4265,10 @@
         <v>54</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D26" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -4279,7 +4279,7 @@
         <v>57</v>
       </c>
       <c r="D27" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -4287,10 +4287,10 @@
         <v>58</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D28" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -4298,10 +4298,10 @@
         <v>60</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D29" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -4312,7 +4312,7 @@
         <v>63</v>
       </c>
       <c r="D30" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -4320,10 +4320,10 @@
         <v>64</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D31" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -4331,10 +4331,10 @@
         <v>66</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D32" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -4342,10 +4342,10 @@
         <v>68</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D33" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -4353,10 +4353,10 @@
         <v>70</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D34" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -4364,10 +4364,10 @@
         <v>72</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D35" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -4375,10 +4375,10 @@
         <v>74</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D36" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -4386,10 +4386,10 @@
         <v>76</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D37" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -4397,10 +4397,10 @@
         <v>78</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D38" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -4408,10 +4408,10 @@
         <v>80</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D39" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -4419,10 +4419,10 @@
         <v>82</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D40" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -4433,7 +4433,7 @@
         <v>85</v>
       </c>
       <c r="D41" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -4444,7 +4444,7 @@
         <v>87</v>
       </c>
       <c r="D42" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -4455,7 +4455,7 @@
         <v>89</v>
       </c>
       <c r="D43" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -4463,10 +4463,10 @@
         <v>90</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D44" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -4474,10 +4474,10 @@
         <v>92</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D45" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -4485,10 +4485,10 @@
         <v>94</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D46" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -4496,10 +4496,10 @@
         <v>96</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D47" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -4507,10 +4507,10 @@
         <v>98</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D48" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -4518,10 +4518,10 @@
         <v>100</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D49" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -4529,10 +4529,10 @@
         <v>102</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D50" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -4540,10 +4540,10 @@
         <v>104</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D51" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -4551,10 +4551,10 @@
         <v>106</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D52" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -4562,10 +4562,10 @@
         <v>108</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D53" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -4576,7 +4576,7 @@
         <v>111</v>
       </c>
       <c r="D54" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -4584,10 +4584,10 @@
         <v>112</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D55" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -4598,7 +4598,7 @@
         <v>115</v>
       </c>
       <c r="D56" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -4606,10 +4606,10 @@
         <v>116</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D57" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
@@ -4617,10 +4617,10 @@
         <v>118</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D58" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -4628,10 +4628,10 @@
         <v>120</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D59" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -4642,260 +4642,260 @@
         <v>123</v>
       </c>
       <c r="D60" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>506</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="D61" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>125</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="D62" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D63" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D64" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>131</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="D65" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D66" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D67" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>137</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="D68" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D69" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>141</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="D70" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>143</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="D71" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>145</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="D72" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D73" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D74" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D75" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D76" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
+        <v>155</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>157</v>
-      </c>
       <c r="D77" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D78" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D79" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D80" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>163</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="D81" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D82" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D83" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -4903,1125 +4903,1125 @@
         <v>5</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D84" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D85" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D86" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
+        <v>174</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>176</v>
-      </c>
       <c r="D87" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D88" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>178</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>180</v>
-      </c>
       <c r="D89" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D90" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
+        <v>182</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="D91" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D92" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D93" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D94" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D95" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D96" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D97" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
+        <v>196</v>
+      </c>
+      <c r="B98" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>198</v>
-      </c>
       <c r="D98" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D99" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D100" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
+        <v>202</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>204</v>
-      </c>
       <c r="D101" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D102" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D103" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D104" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
+        <v>214</v>
+      </c>
+      <c r="B107" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>216</v>
-      </c>
       <c r="D107" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D108" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D109" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
+        <v>220</v>
+      </c>
+      <c r="B110" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>222</v>
-      </c>
       <c r="D110" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
+        <v>222</v>
+      </c>
+      <c r="B111" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="D111" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D112" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
+        <v>226</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B113" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="D113" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D114" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D115" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
+        <v>232</v>
+      </c>
+      <c r="B116" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="B116" s="2" t="s">
-        <v>234</v>
-      </c>
       <c r="D116" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D117" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
+        <v>236</v>
+      </c>
+      <c r="B118" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="B118" s="2" t="s">
-        <v>238</v>
-      </c>
       <c r="D118" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
+        <v>238</v>
+      </c>
+      <c r="B119" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B119" s="2" t="s">
-        <v>240</v>
-      </c>
       <c r="D119" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
+        <v>240</v>
+      </c>
+      <c r="B120" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>242</v>
-      </c>
       <c r="D120" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
+        <v>242</v>
+      </c>
+      <c r="B121" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B121" s="2" t="s">
-        <v>244</v>
-      </c>
       <c r="D121" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D122" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
+        <v>246</v>
+      </c>
+      <c r="B123" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>248</v>
-      </c>
       <c r="D123" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D124" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
+        <v>250</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B125" s="2" t="s">
-        <v>252</v>
-      </c>
       <c r="D125" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D126" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
+        <v>254</v>
+      </c>
+      <c r="B127" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B127" s="2" t="s">
-        <v>256</v>
-      </c>
       <c r="D127" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D128" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
+        <v>258</v>
+      </c>
+      <c r="B129" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B129" s="2" t="s">
-        <v>260</v>
-      </c>
       <c r="D129" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D130" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D131" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D132" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D133" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D134" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D135" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D136" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D137" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D138" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
+        <v>278</v>
+      </c>
+      <c r="B139" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="B139" s="2" t="s">
-        <v>280</v>
-      </c>
       <c r="D139" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
+        <v>280</v>
+      </c>
+      <c r="B140" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="B140" s="2" t="s">
-        <v>282</v>
-      </c>
       <c r="D140" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D141" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
+        <v>284</v>
+      </c>
+      <c r="B142" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="B142" s="2" t="s">
-        <v>286</v>
-      </c>
       <c r="D142" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
+        <v>286</v>
+      </c>
+      <c r="B143" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B143" s="2" t="s">
-        <v>288</v>
-      </c>
       <c r="D143" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
+        <v>288</v>
+      </c>
+      <c r="B144" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="B144" s="2" t="s">
-        <v>290</v>
-      </c>
       <c r="D144" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
+        <v>290</v>
+      </c>
+      <c r="B145" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="B145" s="2" t="s">
-        <v>292</v>
-      </c>
       <c r="D145" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D146" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
+        <v>294</v>
+      </c>
+      <c r="B147" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="B147" s="2" t="s">
-        <v>296</v>
-      </c>
       <c r="D147" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D148" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D149" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D150" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D151" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D152" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
+        <v>306</v>
+      </c>
+      <c r="B153" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="B153" s="2" t="s">
-        <v>308</v>
-      </c>
       <c r="D153" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D154" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
+        <v>310</v>
+      </c>
+      <c r="B155" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="B155" s="2" t="s">
-        <v>312</v>
-      </c>
       <c r="D155" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D156" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
+        <v>314</v>
+      </c>
+      <c r="B157" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="B157" s="2" t="s">
-        <v>316</v>
-      </c>
       <c r="D157" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D158" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D159" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
+        <v>320</v>
+      </c>
+      <c r="B160" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="B160" s="2" t="s">
-        <v>322</v>
-      </c>
       <c r="D160" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
+        <v>322</v>
+      </c>
+      <c r="B161" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="B161" s="2" t="s">
-        <v>324</v>
-      </c>
       <c r="D161" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D162" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D163" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D164" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
+        <v>330</v>
+      </c>
+      <c r="B165" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B165" s="2" t="s">
-        <v>332</v>
-      </c>
       <c r="D165" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D166" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D167" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D168" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D169" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D170" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D171" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D172" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
+        <v>346</v>
+      </c>
+      <c r="B173" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B173" s="2" t="s">
-        <v>348</v>
-      </c>
       <c r="D173" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
+        <v>348</v>
+      </c>
+      <c r="B174" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="B174" s="2" t="s">
-        <v>350</v>
-      </c>
       <c r="D174" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D175" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D176" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
+        <v>354</v>
+      </c>
+      <c r="B177" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="B177" s="2" t="s">
-        <v>356</v>
-      </c>
       <c r="D177" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
+        <v>356</v>
+      </c>
+      <c r="B178" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="B178" s="2" t="s">
-        <v>358</v>
-      </c>
       <c r="D178" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
+        <v>358</v>
+      </c>
+      <c r="B179" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="B179" s="2" t="s">
-        <v>360</v>
-      </c>
       <c r="D179" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D186" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B187" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="D187" t="s">
         <v>503</v>
-      </c>
-      <c r="D187" t="s">
-        <v>505</v>
       </c>
     </row>
   </sheetData>
